--- a/ward_rules.xlsx
+++ b/ward_rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ThanhHuy/Desktop/antibiogram_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADECD08-A927-5346-9855-A1C897596BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF98042F-EA83-794D-892D-6E28B05D2D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{712864EC-5501-C64F-A416-E7BEB35D16A6}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="10000" windowHeight="16940" xr2:uid="{712864EC-5501-C64F-A416-E7BEB35D16A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>WARD</t>
   </si>
@@ -56,17 +56,146 @@
     <t>Gây Mê Hồi Sức</t>
   </si>
   <si>
-    <t>K12</t>
-  </si>
-  <si>
-    <t>Hồi Sức Tích Cực (ICU)</t>
+    <t>K01</t>
+  </si>
+  <si>
+    <t>Khám Bệnh</t>
+  </si>
+  <si>
+    <t>Khoa khám bệnh</t>
+  </si>
+  <si>
+    <t>K04.1</t>
+  </si>
+  <si>
+    <t>Nội Tim Mạch</t>
+  </si>
+  <si>
+    <t>K04.3</t>
+  </si>
+  <si>
+    <t>Tim Mạch Can Thiệp</t>
+  </si>
+  <si>
+    <t>k04.4</t>
+  </si>
+  <si>
+    <t>Khoa điều trị rối loạn nhịp</t>
+  </si>
+  <si>
+    <t>K05</t>
+  </si>
+  <si>
+    <t>Nội Tiêu Hóa</t>
+  </si>
+  <si>
+    <t>K06</t>
+  </si>
+  <si>
+    <t>Nội Cơ Xương Khớp</t>
+  </si>
+  <si>
+    <t>K07</t>
+  </si>
+  <si>
+    <t>Thận - Thận Nhân Tạo</t>
+  </si>
+  <si>
+    <t>K08</t>
+  </si>
+  <si>
+    <t>Nội Tiết</t>
+  </si>
+  <si>
+    <t>K11</t>
+  </si>
+  <si>
+    <t>Bệnh Nhiệt Đới</t>
+  </si>
+  <si>
+    <t>K14</t>
+  </si>
+  <si>
+    <t>Nội Thần Kinh</t>
+  </si>
+  <si>
+    <t>K19</t>
+  </si>
+  <si>
+    <t>Ngoại Tổng Quát</t>
+  </si>
+  <si>
+    <t>K20</t>
+  </si>
+  <si>
+    <t>Ngoại Thần Kinh</t>
+  </si>
+  <si>
+    <t>Ngoại Lồng ngực - Mạch máu</t>
+  </si>
+  <si>
+    <t>K21</t>
+  </si>
+  <si>
+    <t>K23</t>
+  </si>
+  <si>
+    <t>Ngoại Thận Tiết Niệu</t>
+  </si>
+  <si>
+    <t>K24</t>
+  </si>
+  <si>
+    <t>Chấn Thương Chỉnh Hình</t>
+  </si>
+  <si>
+    <t>K25</t>
+  </si>
+  <si>
+    <t>Bỏng - Tạo Hình Thẩm Mỹ</t>
+  </si>
+  <si>
+    <t>K27</t>
+  </si>
+  <si>
+    <t>K48.1</t>
+  </si>
+  <si>
+    <t>Đột Qụy</t>
+  </si>
+  <si>
+    <t>K48</t>
+  </si>
+  <si>
+    <t>Phụ Sản</t>
+  </si>
+  <si>
+    <t>K28</t>
+  </si>
+  <si>
+    <t>Tai Mũi Họng</t>
+  </si>
+  <si>
+    <t>Răng Hàm Mặt</t>
+  </si>
+  <si>
+    <t>K29</t>
+  </si>
+  <si>
+    <t>K33</t>
+  </si>
+  <si>
+    <t>Ung Bướu</t>
+  </si>
+  <si>
+    <t>Hồi Sức T.Cực - C.Độc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -94,6 +223,13 @@
       <color rgb="FF000000"/>
       <name val="-webkit-standard"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -103,10 +239,45 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -115,11 +286,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,11 +630,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B20765A-982C-074C-B06D-FE84231E2788}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18">
@@ -489,45 +665,189 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-    </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
